--- a/ML Algorithm/data/_processed/Y labels/column_flushing_vacp_workload.xlsx
+++ b/ML Algorithm/data/_processed/Y labels/column_flushing_vacp_workload.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Operators" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Legend &amp; VACP Reference" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Step Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operators" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; VACP Reference" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operators'!$A$1:$K$215</definedName>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -120,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +161,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1585,11 +1589,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
@@ -2037,11 +2041,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -2262,11 +2266,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -2585,11 +2589,11 @@
         </is>
       </c>
       <c r="I45" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr"/>
@@ -2630,11 +2634,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -2771,11 +2775,11 @@
         </is>
       </c>
       <c r="I49" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr"/>
@@ -2816,11 +2820,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -3045,11 +3049,11 @@
         </is>
       </c>
       <c r="I55" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr"/>
@@ -3090,11 +3094,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
@@ -3407,11 +3411,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
@@ -4090,11 +4094,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
@@ -4135,11 +4139,11 @@
         </is>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr"/>
@@ -4634,11 +4638,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
@@ -4679,11 +4683,11 @@
         </is>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr"/>
@@ -5092,11 +5096,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
@@ -5321,11 +5325,11 @@
         </is>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr"/>
@@ -6830,11 +6834,11 @@
         </is>
       </c>
       <c r="I138" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K138" s="8" t="inlineStr"/>
@@ -6875,11 +6879,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
@@ -8114,11 +8118,11 @@
         </is>
       </c>
       <c r="I166" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr"/>
@@ -9396,11 +9400,11 @@
         </is>
       </c>
       <c r="I194" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K194" s="6" t="inlineStr"/>
@@ -9766,11 +9770,11 @@
         </is>
       </c>
       <c r="I202" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J202" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K202" s="8" t="inlineStr"/>
@@ -9811,11 +9815,11 @@
         </is>
       </c>
       <c r="I203" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
@@ -10271,11 +10275,11 @@
         </is>
       </c>
       <c r="I213" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J213" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K213" s="8" t="inlineStr"/>
@@ -10316,11 +10320,11 @@
         </is>
       </c>
       <c r="I214" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr"/>
@@ -10734,39 +10738,48 @@
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Step ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Step description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Operators</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>MWI_step</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>MWI_max_recorded</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>p_normalized</t>
         </is>
@@ -10790,10 +10803,10 @@
         <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="F2" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -10817,13 +10830,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>32.1</v>
+        <v>19.9</v>
       </c>
       <c r="F3" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.188713</v>
+        <v>0.121713</v>
       </c>
     </row>
     <row r="4">
@@ -10844,13 +10857,13 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>52.8</v>
+        <v>44.5</v>
       </c>
       <c r="F4" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.310406</v>
+        <v>0.272171</v>
       </c>
     </row>
     <row r="5">
@@ -10871,13 +10884,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>42.7</v>
+        <v>39.5</v>
       </c>
       <c r="F5" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.251029</v>
+        <v>0.24159</v>
       </c>
     </row>
     <row r="6">
@@ -10898,13 +10911,13 @@
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>42.7</v>
+        <v>39.5</v>
       </c>
       <c r="F6" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.251029</v>
+        <v>0.24159</v>
       </c>
     </row>
     <row r="7">
@@ -10925,13 +10938,13 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>38.6</v>
+        <v>35.4</v>
       </c>
       <c r="F7" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.226925</v>
+        <v>0.216514</v>
       </c>
     </row>
     <row r="8">
@@ -10955,10 +10968,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.057613</v>
+        <v>0.059939</v>
       </c>
     </row>
     <row r="9">
@@ -10982,10 +10995,10 @@
         <v>8.6</v>
       </c>
       <c r="F9" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.050558</v>
+        <v>0.052599</v>
       </c>
     </row>
     <row r="10">
@@ -11009,10 +11022,10 @@
         <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.276308</v>
+        <v>0.287462</v>
       </c>
     </row>
     <row r="11">
@@ -11033,13 +11046,13 @@
         <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>108.4</v>
+        <v>101.3</v>
       </c>
       <c r="F11" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6372719999999999</v>
+        <v>0.619572</v>
       </c>
     </row>
     <row r="12">
@@ -11063,10 +11076,10 @@
         <v>24.2</v>
       </c>
       <c r="F12" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.142269</v>
+        <v>0.148012</v>
       </c>
     </row>
     <row r="13">
@@ -11090,10 +11103,10 @@
         <v>15.7</v>
       </c>
       <c r="F13" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09229900000000001</v>
+        <v>0.096024</v>
       </c>
     </row>
     <row r="14">
@@ -11114,13 +11127,13 @@
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="F14" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.156379</v>
+        <v>0.156575</v>
       </c>
     </row>
     <row r="15">
@@ -11141,13 +11154,13 @@
         <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>55.4</v>
+        <v>43.2</v>
       </c>
       <c r="F15" t="n">
-        <v>170.1</v>
+        <v>163.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.325691</v>
+        <v>0.26422</v>
       </c>
     </row>
   </sheetData>
